--- a/data/trans_dic/P80_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P80_R-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,83</t>
+          <t>0,69; 3,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,66</t>
+          <t>1,05; 3,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,6</t>
+          <t>1,1; 2,9</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,4</t>
+          <t>0,81; 3,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,02</t>
+          <t>1,36; 4,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,31</t>
+          <t>1,37; 3,38</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,93</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 4,31</t>
+          <t>0,39; 4,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 1,0</t>
+          <t>0,22; 1,59</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,63</t>
+          <t>1,99; 4,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,03</t>
+          <t>0,88; 2,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,01</t>
+          <t>1,65; 3,21</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 5,09</t>
+          <t>1,89; 6,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,1</t>
+          <t>0,88; 2,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,74</t>
+          <t>1,48; 3,35</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,08; 8,15</t>
+          <t>0,72; 8,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,7</t>
+          <t>0,07; 0,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,93</t>
+          <t>0,25; 1,89</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,59</t>
+          <t>1,72; 2,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,67</t>
+          <t>1,07; 1,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,0</t>
+          <t>1,5; 2,2</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>8999</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>8980</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15681</t>
+          <t>17979</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2526; 14270</t>
+          <t>3766; 18303</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4851; 16351</t>
+          <t>5132; 16201</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9820; 24739</t>
+          <t>11427; 30051</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7544</t>
+          <t>8237</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10556</t>
+          <t>11459</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18100</t>
+          <t>19696</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3034; 15301</t>
+          <t>3885; 17534</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5474; 19185</t>
+          <t>5763; 20104</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10462; 27604</t>
+          <t>12372; 30556</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2161</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>4579</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6215</t>
+          <t>0; 5582</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>327; 7187</t>
+          <t>734; 9210</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>232; 8317</t>
+          <t>1467; 10493</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>30905</t>
+          <t>34195</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10830</t>
+          <t>12391</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41736</t>
+          <t>46586</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19504; 47887</t>
+          <t>22483; 49303</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4296; 19851</t>
+          <t>7533; 20711</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27014; 60462</t>
+          <t>32833; 63812</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13479</t>
+          <t>18651</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10514</t>
+          <t>12499</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23993</t>
+          <t>31150</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7716; 24174</t>
+          <t>10711; 35046</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6087; 17626</t>
+          <t>7340; 20251</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16651; 36073</t>
+          <t>20753; 46870</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>4998</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6940</t>
+          <t>8673</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>187; 19594</t>
+          <t>1719; 19174</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>558; 5334</t>
+          <t>611; 5572</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2184; 19317</t>
+          <t>2685; 20426</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>64274</t>
+          <t>77778</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>45314</t>
+          <t>50884</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>109588</t>
+          <t>128662</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>45820; 87294</t>
+          <t>59173; 101470</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>33280; 59811</t>
+          <t>38661; 64993</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>88722; 138954</t>
+          <t>106130; 155457</t>
         </is>
       </c>
     </row>
